--- a/data/trans_bre/IP2001-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 9,01</t>
+          <t>-9,23; 9,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 3,32</t>
+          <t>-17,22; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 14,94</t>
+          <t>-6,2; 14,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,37</t>
+          <t>-1,86; 6,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,07; 332,2</t>
+          <t>-72,57; 292,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-83,4; 49,1</t>
+          <t>-83,03; 36,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 221,02</t>
+          <t>-39,61; 221,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 2,74</t>
+          <t>-14,41; 2,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 10,28</t>
+          <t>-6,33; 9,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 6,28</t>
+          <t>-6,66; 6,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -0,31</t>
+          <t>-11,81; -0,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 26,81</t>
+          <t>-64,06; 18,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,55; 127,26</t>
+          <t>-40,44; 115,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,2; 126,07</t>
+          <t>-59,66; 163,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-95,5; 29,76</t>
+          <t>-97,08; 4,22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 3,53</t>
+          <t>-5,29; 3,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 9,51</t>
+          <t>-5,02; 10,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 8,46</t>
+          <t>-3,1; 8,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 8,54</t>
+          <t>-10,21; 8,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 518,8</t>
+          <t>-71,41; 737,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 229,55</t>
+          <t>-74,34; 265,75</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 7,05</t>
+          <t>-4,11; 6,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 8,5</t>
+          <t>-8,19; 9,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 11,26</t>
+          <t>-10,25; 11,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 6,49</t>
+          <t>-9,96; 6,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 499,12</t>
+          <t>-71,83; 588,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,32; 128,52</t>
+          <t>-55,84; 150,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,23; 81,93</t>
+          <t>-42,68; 93,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 24,71</t>
+          <t>-1,73; 25,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 25,29</t>
+          <t>-2,13; 25,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 5,15</t>
+          <t>-18,9; 5,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 1,36</t>
+          <t>-16,88; 3,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 494,1</t>
+          <t>-20,43; 547,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 477,95</t>
+          <t>-25,5; 418,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-78,05; 51,11</t>
+          <t>-76,82; 65,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-88,08; 44,37</t>
+          <t>-85,43; 62,29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 6,47</t>
+          <t>-1,98; 7,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 1,31</t>
+          <t>-20,39; 0,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,01; 15,5</t>
+          <t>0,69; 14,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 9,14</t>
+          <t>-3,92; 9,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,79; 30,13</t>
+          <t>-87,84; 20,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 2,74</t>
+          <t>-5,94; 2,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,63</t>
+          <t>-7,32; 3,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 2,67</t>
+          <t>-6,61; 2,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 2,69</t>
+          <t>-9,43; 2,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-79,75; 80,71</t>
+          <t>-77,91; 64,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 54,68</t>
+          <t>-70,94; 76,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-73,79; 65,74</t>
+          <t>-68,82; 73,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 43,85</t>
+          <t>-66,88; 41,15</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 9,75</t>
+          <t>-2,09; 9,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 6,32</t>
+          <t>-2,43; 6,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 7,35</t>
+          <t>-4,38; 7,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,72</t>
+          <t>-2,12; 3,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 148,79</t>
+          <t>-18,58; 139,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 179,14</t>
+          <t>-32,32; 200,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 86,09</t>
+          <t>-31,92; 93,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,96</t>
+          <t>-1,99; 2,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,38</t>
+          <t>-2,55; 2,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,39</t>
+          <t>-1,68; 3,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,54</t>
+          <t>-3,89; 0,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 43,16</t>
+          <t>-21,89; 40,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 29,64</t>
+          <t>-23,8; 34,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 40,05</t>
+          <t>-15,82; 41,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 12,44</t>
+          <t>-52,81; 12,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 9,27</t>
+          <t>-8,56; 8,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 2,3</t>
+          <t>-16,35; 2,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 14,97</t>
+          <t>-6,99; 14,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,26</t>
+          <t>-2,09; 7,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,57; 292,93</t>
+          <t>-73,69; 247,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-83,03; 36,44</t>
+          <t>-82,78; 39,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 221,36</t>
+          <t>-42,96; 206,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 2,24</t>
+          <t>-13,91; 2,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 9,61</t>
+          <t>-6,86; 8,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 6,31</t>
+          <t>-6,86; 5,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -0,56</t>
+          <t>-11,68; -0,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 18,6</t>
+          <t>-64,63; 18,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 115,32</t>
+          <t>-44,19; 101,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 163,81</t>
+          <t>-60,67; 129,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-97,08; 4,22</t>
+          <t>-95,11; 5,87</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 3,52</t>
+          <t>-4,83; 3,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 10,12</t>
+          <t>-4,8; 10,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 8,41</t>
+          <t>-3,3; 8,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 8,34</t>
+          <t>-10,21; 7,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,41; 737,34</t>
+          <t>-62,78; 758,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,34; 265,75</t>
+          <t>-73,44; 197,63</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 6,97</t>
+          <t>-4,54; 6,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 9,37</t>
+          <t>-7,77; 9,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 11,96</t>
+          <t>-9,24; 12,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 6,21</t>
+          <t>-9,14; 5,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,83; 588,51</t>
+          <t>-75,39; 655,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 150,09</t>
+          <t>-54,24; 147,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 93,68</t>
+          <t>-40,66; 109,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 25,71</t>
+          <t>-1,47; 26,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 25,21</t>
+          <t>-2,18; 24,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 5,9</t>
+          <t>-17,91; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 3,7</t>
+          <t>-18,5; 1,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 547,59</t>
+          <t>-23,47; 466,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 418,21</t>
+          <t>-17,31; 435,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-76,82; 65,99</t>
+          <t>-76,84; 75,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-85,43; 62,29</t>
+          <t>-87,33; 57,41</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 7,31</t>
+          <t>-2,04; 6,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 0,14</t>
+          <t>-18,83; 1,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 14,46</t>
+          <t>1,28; 15,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 9,49</t>
+          <t>-3,86; 9,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,84; 20,82</t>
+          <t>-85,7; 45,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 2,62</t>
+          <t>-6,52; 2,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,14</t>
+          <t>-7,67; 3,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 2,74</t>
+          <t>-7,46; 2,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,43</t>
+          <t>-8,72; 2,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 64,32</t>
+          <t>-78,33; 86,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-70,94; 76,28</t>
+          <t>-70,17; 80,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 73,04</t>
+          <t>-71,15; 69,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 41,15</t>
+          <t>-66,45; 47,9</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 9,24</t>
+          <t>-1,49; 9,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 6,53</t>
+          <t>-2,78; 6,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 7,47</t>
+          <t>-4,41; 7,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,27</t>
+          <t>-1,99; 3,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 139,66</t>
+          <t>-15,64; 156,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 200,46</t>
+          <t>-40,14; 168,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 93,51</t>
+          <t>-30,0; 82,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,86</t>
+          <t>-2,12; 2,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,8</t>
+          <t>-2,93; 2,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,52</t>
+          <t>-1,77; 3,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,51</t>
+          <t>-3,78; 0,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 40,7</t>
+          <t>-23,13; 38,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 34,93</t>
+          <t>-26,33; 30,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 41,19</t>
+          <t>-16,08; 39,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 12,39</t>
+          <t>-53,2; 7,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2001-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2001-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 8,71</t>
+          <t>-8,53; 9,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 2,57</t>
+          <t>-17,14; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 14,93</t>
+          <t>-6,03; 14,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 7,07</t>
+          <t>-2,7; 7,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 247,89</t>
+          <t>-71,07; 332,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,78; 39,82</t>
+          <t>-83,4; 49,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 206,36</t>
+          <t>-35,27; 221,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,82</t>
+          <t>-4,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-69,29%</t>
+          <t>-64,01%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 2,31</t>
+          <t>-14,32; 2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 8,77</t>
+          <t>-6,26; 10,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 5,9</t>
+          <t>-6,0; 6,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -0,22</t>
+          <t>-10,92; 0,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,63; 18,99</t>
+          <t>-62,02; 26,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 101,84</t>
+          <t>-39,55; 127,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 129,59</t>
+          <t>-56,2; 126,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-95,11; 5,87</t>
+          <t>-93,62; 52,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 3,39</t>
+          <t>-4,74; 3,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 10,13</t>
+          <t>-5,08; 9,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,23</t>
+          <t>-2,68; 8,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 7,68</t>
+          <t>-6,75; 9,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 758,2</t>
+          <t>-70,37; 518,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,44; 197,63</t>
+          <t>-61,57; 260,78</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-10,94%</t>
+          <t>-14,39%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 6,54</t>
+          <t>-4,32; 7,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 9,65</t>
+          <t>-8,58; 8,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 12,69</t>
+          <t>-9,76; 11,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 5,94</t>
+          <t>-9,14; 6,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,39; 655,73</t>
+          <t>-75,77; 499,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 147,93</t>
+          <t>-58,32; 128,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 109,47</t>
+          <t>-44,23; 81,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,18</t>
+          <t>-7,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-51,43%</t>
+          <t>-53,19%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 26,04</t>
+          <t>-2,36; 24,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 24,57</t>
+          <t>-1,99; 25,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 6,52</t>
+          <t>-18,86; 5,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 1,89</t>
+          <t>-19,33; 1,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 466,12</t>
+          <t>-23,11; 494,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 435,11</t>
+          <t>-16,46; 477,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 75,43</t>
+          <t>-78,05; 51,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 57,41</t>
+          <t>-88,47; 36,14</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 6,34</t>
+          <t>-1,92; 6,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 1,14</t>
+          <t>-18,45; 1,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 15,76</t>
+          <t>0,01; 15,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 9,63</t>
+          <t>-3,14; 9,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,7; 45,94</t>
+          <t>-85,79; 30,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,2</t>
+          <t>-4,11</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-31,21%</t>
+          <t>-35,9%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 2,63</t>
+          <t>-6,19; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 3,56</t>
+          <t>-7,7; 2,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 2,6</t>
+          <t>-7,72; 2,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 2,84</t>
+          <t>-9,98; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-78,33; 86,53</t>
+          <t>-79,75; 80,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-70,17; 80,62</t>
+          <t>-75,74; 54,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-71,15; 69,85</t>
+          <t>-73,79; 65,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-66,45; 47,9</t>
+          <t>-67,39; 35,12</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 9,62</t>
+          <t>-2,02; 9,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 6,13</t>
+          <t>-2,44; 6,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 7,42</t>
+          <t>-4,57; 7,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,69</t>
+          <t>-1,53; 3,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 156,18</t>
+          <t>-22,57; 148,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 168,98</t>
+          <t>-36,67; 179,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 82,13</t>
+          <t>-32,7; 86,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-27,53%</t>
+          <t>-25,49%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,7</t>
+          <t>-2,07; 2,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,44</t>
+          <t>-2,77; 2,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,35</t>
+          <t>-1,81; 3,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,4</t>
+          <t>-3,78; 0,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 38,11</t>
+          <t>-22,38; 43,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 30,69</t>
+          <t>-25,37; 29,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 39,56</t>
+          <t>-16,83; 40,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 7,53</t>
+          <t>-50,31; 12,02</t>
         </is>
       </c>
     </row>
